--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
@@ -32,9 +32,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -464,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>أ. محمد الرفاعي</v>
+        <v>محمد عبد الله وصل الرفاعي</v>
       </c>
       <c r="C4" t="str">
         <v>مبنى 5000</v>
@@ -504,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>د. فهد السعدي</v>
+        <v>فهد مصلح منيف السعدي</v>
       </c>
       <c r="C6" t="str">
         <v>51</v>
@@ -524,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>د. نواف الحميدي</v>
+        <v>نواف محسن عايض الحميدي</v>
       </c>
       <c r="C7" t="str">
         <v>48</v>
@@ -544,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>أ. هتان الشريف</v>
+        <v>هتان عبدالعزيز راجح الشريف</v>
       </c>
       <c r="C8" t="str">
         <v>58</v>
@@ -564,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>د. طارق حلمي</v>
+        <v>طارق حلمى عبدالنبي علي</v>
       </c>
       <c r="C9" t="str">
         <v>50</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>د. زياد المطيري</v>
+        <v>زياد حمود عبدالعزيز العضيله المطيري</v>
       </c>
       <c r="C5" t="str">
         <v>59</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>طارق حلمى عبدالنبي علي</v>
+        <v>د. طارق حلمي</v>
       </c>
       <c r="C9" t="str">
         <v>50</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>د. طارق حلمي</v>
+        <v>طارق حلمى عبدالنبي علي</v>
       </c>
       <c r="C9" t="str">
         <v>50</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طلاب.xlsx
@@ -464,7 +464,7 @@
         <v>محمد عبد الله وصل الرفاعي</v>
       </c>
       <c r="C4" t="str">
-        <v>مبنى 5000</v>
+        <v>5000</v>
       </c>
       <c r="D4" t="str">
         <v>الفترة الأولى</v>
@@ -484,7 +484,7 @@
         <v>زياد حمود عبدالعزيز العضيله المطيري</v>
       </c>
       <c r="C5" t="str">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="str">
         <v>الفترة الأولى</v>
